--- a/employees.xlsx
+++ b/employees.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alnaseem\Desktop\employees_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6690"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>التسلسل</t>
   </si>
@@ -95,43 +95,13 @@
     <t>الصافي</t>
   </si>
   <si>
-    <t>التوقيع</t>
-  </si>
-  <si>
-    <t>الاء قابل سلمان</t>
-  </si>
-  <si>
-    <t>ر. كتاب طابعة اقدم</t>
-  </si>
-  <si>
-    <t>خامسة</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>مشتاق اسماعيل ابراهيم حسين الا</t>
-  </si>
-  <si>
-    <t>ر. حراس اقدم اول</t>
-  </si>
-  <si>
-    <t>رابعة</t>
-  </si>
-  <si>
-    <t>حيدر كامل بدر عيدان المعموري</t>
-  </si>
-  <si>
-    <t>ر.حرفين اقدم اول</t>
-  </si>
-  <si>
-    <t>فاطمة كريم حسين سعيدي</t>
+    <t>المجموع.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -192,7 +162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -207,6 +177,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -490,9 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -564,315 +538,227 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>17</v>
+      <c r="W1" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="2" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>862</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="4">
-        <v>510000</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>76500</v>
-      </c>
-      <c r="K2" s="4">
-        <v>20000</v>
-      </c>
-      <c r="L2" s="4">
-        <v>102000</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>708500</v>
-      </c>
-      <c r="S2" s="4">
-        <v>51000</v>
-      </c>
-      <c r="T2" s="4">
-        <v>28026</v>
-      </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4">
-        <v>1275</v>
-      </c>
-      <c r="W2" s="4">
-        <v>80301</v>
-      </c>
-      <c r="X2" s="4">
-        <v>628199</v>
-      </c>
-      <c r="Y2" s="3"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>157</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="4">
-        <v>589000</v>
-      </c>
-      <c r="G3" s="4">
-        <v>50000</v>
-      </c>
-      <c r="H3" s="4">
-        <v>20000</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>147250</v>
-      </c>
-      <c r="K3" s="4">
-        <v>20000</v>
-      </c>
-      <c r="L3" s="4">
-        <v>176700</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <v>1002950</v>
-      </c>
-      <c r="S3" s="4">
-        <v>58900</v>
-      </c>
-      <c r="T3" s="4">
-        <v>8370</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4">
-        <v>1472.5</v>
-      </c>
-      <c r="W3" s="4">
-        <v>68743</v>
-      </c>
-      <c r="X3" s="4">
-        <v>934207</v>
-      </c>
-      <c r="Y3" s="3"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>1057</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="4">
-        <v>589000</v>
-      </c>
-      <c r="G4" s="4">
-        <v>50000</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>88350</v>
-      </c>
-      <c r="K4" s="4">
-        <v>20000</v>
-      </c>
-      <c r="L4" s="4">
-        <v>176700</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4">
-        <v>924050</v>
-      </c>
-      <c r="S4" s="4">
-        <v>58900</v>
-      </c>
-      <c r="T4" s="4">
-        <v>13370</v>
-      </c>
-      <c r="U4" s="4">
-        <v>185400</v>
-      </c>
-      <c r="V4" s="4">
-        <v>1472.5</v>
-      </c>
-      <c r="W4" s="4">
-        <v>259143</v>
-      </c>
-      <c r="X4" s="4">
-        <v>664907</v>
-      </c>
-      <c r="Y4" s="3"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>1225</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4">
-        <v>589000</v>
-      </c>
-      <c r="G5" s="4">
-        <v>50000</v>
-      </c>
-      <c r="H5" s="4">
-        <v>20000</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
-        <v>88350</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>176700</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4">
-        <v>924050</v>
-      </c>
-      <c r="S5" s="4">
-        <v>58900</v>
-      </c>
-      <c r="T5" s="4">
-        <v>8370</v>
-      </c>
-      <c r="U5" s="4">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4">
-        <v>1472.5</v>
-      </c>
-      <c r="W5" s="4">
-        <v>68743</v>
-      </c>
-      <c r="X5" s="4">
-        <v>855307</v>
-      </c>
-      <c r="Y5" s="3"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="3"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="3"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="3"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="3"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
